--- a/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_FENERBAHCE BEKO ISTANBUL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_FENERBAHCE BEKO ISTANBUL.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>12.9767</v>
+        <v>12.1533</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1047</v>
+        <v>7.0735</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8718</v>
+        <v>5.0801</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4123</v>
+        <v>10.2643</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4713</v>
+        <v>2.6606</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9410999999999998</v>
+        <v>7.603599999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>6.7374</v>
+        <v>9.993399999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3217</v>
+        <v>3.7728</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4158</v>
+        <v>6.220599999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.3249</v>
+        <v>0.2709999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.8504</v>
+        <v>-1.1121</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4745</v>
+        <v>1.3829</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4550000000000001</v>
+        <v>-0.6824000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.777</v>
+        <v>-4.5495</v>
       </c>
       <c r="R2" t="n">
-        <v>5.2319</v>
+        <v>3.867</v>
       </c>
       <c r="S2" t="n">
-        <v>8.0192</v>
+        <v>0.2513000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>6.2625</v>
+        <v>-0.005600000000000049</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7569</v>
+        <v>0.2568</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0902</v>
+        <v>2.3202</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8818</v>
+        <v>1.6352</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7917</v>
+        <v>0.6851</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.269500000000001</v>
+        <v>8.4864</v>
       </c>
       <c r="E3" t="n">
-        <v>4.361599999999999</v>
+        <v>5.7675</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9079</v>
+        <v>2.7188</v>
       </c>
       <c r="G3" t="n">
-        <v>10.2643</v>
+        <v>3.4123</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6606</v>
+        <v>2.4713</v>
       </c>
       <c r="I3" t="n">
-        <v>7.603599999999999</v>
+        <v>0.9410999999999998</v>
       </c>
       <c r="J3" t="n">
-        <v>9.993399999999999</v>
+        <v>6.7374</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7728</v>
+        <v>5.3217</v>
       </c>
       <c r="L3" t="n">
-        <v>6.220599999999999</v>
+        <v>1.4158</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2709999999999999</v>
+        <v>-3.3249</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1121</v>
+        <v>-2.8504</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3829</v>
+        <v>-0.4745</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6824000000000001</v>
+        <v>0.4550000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.5495</v>
+        <v>-4.777</v>
       </c>
       <c r="R3" t="n">
-        <v>3.867</v>
+        <v>5.2319</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.6325</v>
+        <v>3.5289</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.7175</v>
+        <v>1.9252</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9151</v>
+        <v>1.6036</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3202</v>
+        <v>1.0902</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6352</v>
+        <v>1.8818</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6851</v>
+        <v>-0.7917</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8493</v>
+        <v>8.111699999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5566</v>
+        <v>7.2267</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7074</v>
+        <v>0.8848999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>11.8403</v>
@@ -766,13 +766,13 @@
         <v>9.099</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.0409</v>
+        <v>0.2216000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1605</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.8803</v>
+        <v>-0.2881</v>
       </c>
       <c r="V4" t="n">
         <v>-2.5853</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. SILVA</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0975</v>
+        <v>2.731100000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7094</v>
+        <v>4.8102</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6121</v>
+        <v>-2.0792</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2147</v>
+        <v>8.7514</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2715000000000001</v>
+        <v>-0.9593</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9431999999999999</v>
+        <v>9.710699999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6184</v>
+        <v>12.8258</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8360999999999998</v>
+        <v>2.8346</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7824</v>
+        <v>9.991199999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4036999999999999</v>
+        <v>-4.0743</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5643999999999999</v>
+        <v>-3.7938</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1607999999999999</v>
+        <v>-0.2805000000000002</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.0472</v>
+        <v>-0.9099000000000002</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.5495</v>
+        <v>-8.416500000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5022</v>
+        <v>7.5066</v>
       </c>
       <c r="S5" t="n">
-        <v>2.95</v>
+        <v>0.4099999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4604</v>
+        <v>-0.07409999999999994</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5102</v>
+        <v>0.484</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0201</v>
+        <v>-5.5206</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1802</v>
+        <v>0.475</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.2003</v>
+        <v>-5.9956</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7077000000000009</v>
+        <v>0.9663000000000004</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6399999999999997</v>
+        <v>-0.6040000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3477</v>
+        <v>1.5706</v>
       </c>
       <c r="G6" t="n">
         <v>0.5558000000000005</v>
@@ -922,13 +922,13 @@
         <v>9.099</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1956</v>
+        <v>2.4542</v>
       </c>
       <c r="T6" t="n">
-        <v>0.887</v>
+        <v>0.9227000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3088</v>
+        <v>1.5316</v>
       </c>
       <c r="V6" t="n">
         <v>-2.9536</v>
@@ -955,13 +955,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3204000000000004</v>
+        <v>0.5159999999999997</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4755999999999996</v>
+        <v>-0.5205999999999997</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7959999999999998</v>
+        <v>1.0366</v>
       </c>
       <c r="G7" t="n">
         <v>-1.822</v>
@@ -1000,13 +1000,13 @@
         <v>2.9571</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0041</v>
+        <v>2.1998</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2692</v>
+        <v>1.2245</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7348</v>
+        <v>0.9755</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3167</v>
@@ -1033,13 +1033,13 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2281</v>
+        <v>0.3837</v>
       </c>
       <c r="E8" t="n">
         <v>0.2074</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0207</v>
+        <v>0.1763</v>
       </c>
       <c r="G8" t="n">
         <v>0.1736</v>
@@ -1078,13 +1078,13 @@
         <v>0.455</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0839</v>
+        <v>0.07179999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>0.1556</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2395</v>
+        <v>-0.0838</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3166</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>C. SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1249</v>
+        <v>-0.4398</v>
       </c>
       <c r="E10" t="n">
-        <v>1.999699999999999</v>
+        <v>0.4466000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1245</v>
+        <v>-0.8864000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>8.7514</v>
+        <v>1.2147</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9593</v>
+        <v>0.2715000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>9.710699999999999</v>
+        <v>0.9431999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>12.8258</v>
+        <v>1.6184</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8346</v>
+        <v>0.8360999999999998</v>
       </c>
       <c r="L10" t="n">
-        <v>9.991199999999999</v>
+        <v>0.7824</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.0743</v>
+        <v>-0.4036999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.7938</v>
+        <v>-0.5643999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2805000000000002</v>
+        <v>0.1607999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9099000000000002</v>
+        <v>-2.0472</v>
       </c>
       <c r="Q10" t="n">
-        <v>-8.416500000000001</v>
+        <v>-4.5495</v>
       </c>
       <c r="R10" t="n">
-        <v>7.5066</v>
+        <v>2.5022</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.4459</v>
+        <v>1.4128</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.8846</v>
+        <v>1.1974</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5613</v>
+        <v>0.2153</v>
       </c>
       <c r="V10" t="n">
-        <v>-5.5206</v>
+        <v>-1.0201</v>
       </c>
       <c r="W10" t="n">
-        <v>0.475</v>
+        <v>2.1802</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.9956</v>
+        <v>-3.2003</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3531</v>
+        <v>-2.0066</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1858000000000002</v>
+        <v>-0.1769000000000003</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1673</v>
+        <v>-1.8296</v>
       </c>
       <c r="G11" t="n">
         <v>-4.833699999999999</v>
@@ -1312,13 +1312,13 @@
         <v>7.734</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7997999999999998</v>
+        <v>1.1465</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4557999999999998</v>
+        <v>0.4646999999999997</v>
       </c>
       <c r="U11" t="n">
-        <v>0.344</v>
+        <v>0.6818</v>
       </c>
       <c r="V11" t="n">
         <v>0.08830000000000027</v>
@@ -1345,13 +1345,13 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7606</v>
+        <v>-3.8626</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.962599999999999</v>
+        <v>-2.837</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7979</v>
+        <v>-1.0255</v>
       </c>
       <c r="G12" t="n">
         <v>-6.0497</v>
@@ -1390,13 +1390,13 @@
         <v>4.322</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7421999999999999</v>
+        <v>1.64</v>
       </c>
       <c r="T12" t="n">
-        <v>1.533</v>
+        <v>1.6586</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7907</v>
+        <v>-0.01849999999999997</v>
       </c>
       <c r="V12" t="n">
         <v>1.0018</v>
@@ -1423,13 +1423,13 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.5651</v>
+        <v>-12.7389</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.8579</v>
+        <v>-8.7029</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.7072</v>
+        <v>-4.0359</v>
       </c>
       <c r="G13" t="n">
         <v>-6.6919</v>
@@ -1468,13 +1468,13 @@
         <v>7.5067</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.7369</v>
+        <v>1.0896</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2085</v>
+        <v>0.9465000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5283</v>
+        <v>0.1429999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-3.042</v>
@@ -1501,19 +1501,19 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>3.801099999999998</v>
+        <v>14.4562</v>
       </c>
       <c r="E14" t="n">
-        <v>9.817499999999999</v>
+        <v>12.6905</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.0167</v>
+        <v>1.7663</v>
       </c>
       <c r="G14" t="n">
         <v>16.9707</v>
       </c>
       <c r="H14" t="n">
-        <v>1.266</v>
+        <v>1.265999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>15.70489999999999</v>
@@ -1522,10 +1522,10 @@
         <v>47.1022</v>
       </c>
       <c r="K14" t="n">
-        <v>23.9857</v>
+        <v>23.98569999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>23.11619999999999</v>
+        <v>23.1162</v>
       </c>
       <c r="M14" t="n">
         <v>-30.1309</v>
@@ -1543,16 +1543,16 @@
         <v>-65.9675</v>
       </c>
       <c r="R14" t="n">
-        <v>60.2805</v>
+        <v>60.28050000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>3.770799999999999</v>
+        <v>14.4265</v>
       </c>
       <c r="T14" t="n">
-        <v>6.052400000000001</v>
+        <v>8.925099999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.280900000000001</v>
+        <v>5.501199999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-11.2544</v>
